--- a/data/analysis_ministral_3_14b_panns/multimodal_event_eval_ministral_3_14b_panns_w1_0s_h0_5s.xlsx
+++ b/data/analysis_ministral_3_14b_panns/multimodal_event_eval_ministral_3_14b_panns_w1_0s_h0_5s.xlsx
@@ -115,7 +115,7 @@
     <t>sound: gunshot_or_explosion(96-156), sound: engine(144-240), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: gunshot_visible(168-168), visual: running(120-240), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-120), visual: vehicle_collision(216-240)</t>
   </si>
   <si>
-    <t>sound: engine(0-60), sound: engine(84-192), sound: engine(216-240), sound: gunshot_or_explosion(60-96), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(48-72), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(48-144), visual: suspicious_near_vehicle(0-0)</t>
+    <t>sound: engine(0-240), sound: gunshot_or_explosion(60-96), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(48-72), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(48-144), visual: suspicious_near_vehicle(0-0)</t>
   </si>
   <si>
     <t>sound: engine(24-72), sound: engine(144-240), sound: gunshot_or_explosion(120-144), visual: carrying(144-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-120), visual: gunshot_visible(120-120), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(144-168), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(96-96)</t>
@@ -178,7 +178,7 @@
     <t>sound: engine(36-60), sound: engine(96-240), visual: carrying(0-0), visual: carrying(24-48), visual: enter_or_exit_vehicle(72-72), visual: running(24-24), visual: suspicious_near_vehicle(0-72)</t>
   </si>
   <si>
-    <t>sound: engine(0-36), sound: engine(60-240), visual: enter_or_exit_vehicle(48-240), visual: running(0-0), visual: suspicious_near_vehicle(0-192)</t>
+    <t>sound: engine(0-240), visual: enter_or_exit_vehicle(48-240), visual: running(0-0), visual: suspicious_near_vehicle(0-192)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(48-240), visual: running(0-0), visual: suspicious_near_vehicle(0-192)</t>
